--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_detail_optimization_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_detail_optimization_testcases.xlsx
@@ -268,17 +268,17 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -328,7 +328,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -355,17 +355,17 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
@@ -441,17 +441,17 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
@@ -587,7 +587,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -614,17 +614,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -676,7 +676,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -703,17 +703,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -764,7 +764,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -791,17 +791,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -852,7 +852,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -879,17 +879,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析详情页</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0核心流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -967,7 +967,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -1052,17 +1052,17 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">当前图展示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1138,12 +1138,12 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1224,12 +1224,12 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="L14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="2">
@@ -1310,17 +1310,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">图形状态</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1396,12 +1396,12 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1482,12 +1482,12 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1569,17 +1569,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">不可切换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1655,7 +1655,7 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1742,12 +1742,12 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
@@ -1828,7 +1828,7 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -2001,17 +2001,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">展示范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2087,7 +2087,7 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -2173,12 +2173,12 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置区域</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2259,12 +2259,12 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置区域</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2346,7 +2346,7 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2432,12 +2432,12 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UI展示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2518,7 +2518,7 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
